--- a/iOiO_7-9月社群月曆.xlsx
+++ b/iOiO_7-9月社群月曆.xlsx
@@ -39,7 +39,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -78,11 +78,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FBE9E7"/>
       </patternFill>
     </fill>
@@ -113,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,15 +167,6 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -223,10 +209,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1462,49 +1448,57 @@
       </c>
       <c r="J16" s="10" t="inlineStr"/>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="17" ht="135" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>8/18週</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>8/21（四）</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>產品</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>（待主打產品確認後補入）</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>【TBD — 等8-9月主打產品確認後填入】</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr"/>
-      <c r="I17" s="19" t="inlineStr"/>
-      <c r="J17" s="19" t="inlineStr">
-        <is>
-          <t>⚠️ 待主打產品確認</t>
-        </is>
-      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>這口感，是蒟蒻嗎？——超口感蒟蒻</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>很多人第一次喝iOiO超口感蒟蒻，都會說同一句話：
+「這真的是蒟蒻？」
+是的，蒟蒻。但咀嚼感升級了。
+一般蒟蒻飲料的口感通常很軟，嚼一下就沒了。超口感系列在這件事上認真了一點——每一顆蒟蒻塊的嚼勁明顯一些，喝下去有種真實的飽足感，不是那種喝了半瓶還沒感覺的感覺。
+不想喝含糖飲料，又覺得白開水太無聊，這個可以試試。</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>#iOiO #超口感蒟蒻 #蒟蒻飲 #無負擔飲品 #低卡</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>超口感蒟蒻產品特寫＋蒟蒻塊倒出的質感，強調真實咀嚼感，清爽色系</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="240" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1564,37 +1558,37 @@
       <c r="J18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="135" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>8/25週</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>8/28（四）</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>品牌溫度</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>陪孩子長大的每個夏天</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>每年夏天都比上一個快。
 去年還說要去某個地方，今年暑假轉眼又快結束了。
@@ -1603,17 +1597,17 @@
 明年夏天再見。</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="19" t="inlineStr">
         <is>
           <t>#暑假 #親子 #iOiO #YiBiYaYa #夏天</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
         <is>
           <t>夏日光線、孩子側影或手拿iOiO的溫柔構圖，情感向，不強調產品</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="J19" s="19" t="inlineStr">
         <is>
           <t>季節收尾情感貼文</t>
         </is>
@@ -1776,49 +1770,58 @@
       </c>
       <c r="J22" s="13" t="inlineStr"/>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>9/8週</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>9/11（四）</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>產品</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>（待主打產品確認後補入）</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
-        <is>
-          <t>【TBD — 等8-9月主打產品確認後填入】</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="inlineStr"/>
-      <c r="I23" s="19" t="inlineStr"/>
-      <c r="J23" s="19" t="inlineStr">
-        <is>
-          <t>⚠️ 待主打產品確認</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>元素蒟蒻，因為你的一天不只需要水</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>iOiO元素蒟蒻，有兩個口味。
+Bright Berry，藍莓口味
+Energy Apple，蘋果口味
+系列名字叫「元素」，是因為每一瓶加入了特定的成分——不是靠廣告說的那種，就是你翻到成分表、找得到、看得懂的那些。
+口味是果汁感，蒟蒻塊的嚼感在，不甜膩，帶得出門。
+你的一天喝什麼，可以多一個選擇。</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>#iOiO #元素蒟蒻 #BrightBerry #EnergyApple #蒟蒻飲</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>兩款元素蒟蒻並排，乾淨背景，Bright Berry藍紫色系與Energy Apple蘋果綠對比</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="255" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2094,49 +2097,57 @@
       </c>
       <c r="J28" s="4" t="inlineStr"/>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+    <row r="29" ht="135" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>9/29週</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>10/2（四）</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>產品</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>（待主打產品確認後補入）</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>【TBD — 等8-9月主打產品確認後填入】</t>
-        </is>
-      </c>
-      <c r="H29" s="19" t="inlineStr"/>
-      <c r="I29" s="19" t="inlineStr"/>
-      <c r="J29" s="19" t="inlineStr">
-        <is>
-          <t>⚠️ 待主打產品確認</t>
-        </is>
-      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>連假結束，元素蒟蒻陪你收假</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>雙十連假結束的週四。
+返回工作模式的那一天，通常是最難的那一天。
+iOiO元素蒟蒻——Bright Berry 藍莓口味、Energy Apple 蘋果口味，加了特定成分配方，口感是蒟蒻，喝起來是果汁感。
+不用說什麼特別的話，就是一瓶你可以帶著走的東西。
+收假了，慢慢來。</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>#iOiO #元素蒟蒻 #收假 #週四 #蒟蒻飲</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>辦公桌或包包旁的元素蒟蒻，輕鬆生活感，秋天暖色調</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2157,233 +2168,232 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>圖例說明</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr"/>
+      <c r="B1" s="21" t="inlineStr"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>類型色碼</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr"/>
+      <c r="B2" s="23" t="inlineStr"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>食育</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>食品知識/育兒資訊，高儲存率目標</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>產品</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>商品介紹，全月不超過2篇</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>生活情境</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>親子日常，情感共鳴，帶iOiO自然入鏡</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>互動</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>留言/問答，一季約2-3次</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>品牌故事</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>原料溯源/品質承諾，建立長期信任感</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>品牌溫度</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>情感向，不賣產品，建立品牌黏著度</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="25" t="inlineStr"/>
-      <c r="B9" s="26" t="inlineStr"/>
+      <c r="A9" s="22" t="inlineStr"/>
+      <c r="B9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>發文時間建議</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr"/>
+      <c r="B10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>週二</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>上午9-11點 或 晚上7-9點</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>週四</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>上午9-11點 或 晚上7-9點</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="25" t="inlineStr"/>
-      <c r="B13" s="26" t="inlineStr"/>
+      <c r="A13" s="22" t="inlineStr"/>
+      <c r="B13" s="23" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>內容比例</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr"/>
+      <c r="B14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>食育+生活情境+品牌故事</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>70%（約18篇）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>產品介紹</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>20%（約5篇）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>互動</t>
         </is>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>10%（約3篇）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="25" t="inlineStr"/>
-      <c r="B18" s="26" t="inlineStr"/>
+      <c r="A18" s="22" t="inlineStr"/>
+      <c r="B18" s="23" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>TBD說明</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr"/>
+      <c r="B19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>⚠️ 3篇待補</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>8/21、9/11、10/2 為產品貼文，
-待8-9月主打產品確認後填入</t>
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>✅ 已全部完成</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>8/21 超口感蒟蒻、9/11 元素蒟蒻、10/2 元素蒟蒻（收假情境）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="25" t="inlineStr"/>
-      <c r="B21" s="26" t="inlineStr"/>
+      <c r="A21" s="22" t="inlineStr"/>
+      <c r="B21" s="23" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>追蹤指標（冷啟動期）</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr"/>
+      <c r="B22" s="21" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>優先觀察</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>儲存數 &gt; 觸及 &gt; 留言數</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>原因</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>知識型/食育內容儲存率高，
 演算法視儲存為高價值互動</t>

--- a/iOiO_7-9月社群月曆.xlsx
+++ b/iOiO_7-9月社群月曆.xlsx
@@ -731,25 +731,25 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>YiBiYaYa 益生菌系列登場</t>
+          <t>YiBiYaYa 益生菌系列——一包粉末，加進去就好</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>YiBiYaYa 出了益生菌系列，來說說這個系列是什麼。
-100億益生菌配方，加上維生素C和D——不是靠宣稱，就是老老實實的成分組合。
-口感是果汁飲，不是藥水感，孩子喝起來不會知道「裡面有什麼」。常溫保存，出門帶一包不用擔心冷藏。
-如果你家孩子對果汁的接受度比較高，這個系列可以試試。</t>
+          <t>YiBiYaYa 益生菌系列是粉末包裝，不是飲料罐。
+100億益生菌配方，草莓蘋果或葡萄藍莓口味，撕開一包加進水裡攪一攪——孩子喝起來有水果甜味，不是藥水感，不用哄。
+不加人工色素、不加人工香料，成分表翻開看得懂。一包一份量，書包塞一包帶出門，或是早餐桌上倒進牛奶杯裡都行。
+給孩子喝好的，不用複雜，這樣就夠了。</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>#YiBiYaYa #益生菌 #iOiO #兒童飲品</t>
+          <t>#YiBiYaYa #益生菌 #iOiO #兒童健康 #粉末包裝</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>產品正面+開蓋情境，吉祥物兔子搭配，背景清爽</t>
+          <t>粉末包裝撕開倒入水杯的動作特寫，或產品包裝平鋪，清爽背景</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr"/>

--- a/iOiO_7-9月社群月曆.xlsx
+++ b/iOiO_7-9月社群月曆.xlsx
@@ -731,25 +731,25 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>YiBiYaYa 益生菌系列——一包粉末，加進去就好</t>
+          <t>YiBiYaYa 益生菌系列——撕開，直接吃</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
           <t>YiBiYaYa 益生菌系列是粉末包裝，不是飲料罐。
-100億益生菌配方，草莓蘋果或葡萄藍莓口味，撕開一包加進水裡攪一攪——孩子喝起來有水果甜味，不是藥水感，不用哄。
-不加人工色素、不加人工香料，成分表翻開看得懂。一包一份量，書包塞一包帶出門，或是早餐桌上倒進牛奶杯裡都行。
-給孩子喝好的，不用複雜，這樣就夠了。</t>
+100億益生菌配方，草莓蘋果或葡萄藍莓口味——撕開一包直接倒入口中就好，不用加水、不用沖泡，孩子吃起來是水果甜味，不是藥水感，不用哄。
+不加人工色素、不加人工香料，成分表翻開看得懂。一包一份量，書包塞一包帶出門，下課了撕開就吃。
+給孩子好的，不用麻煩。</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>#YiBiYaYa #益生菌 #iOiO #兒童健康 #粉末包裝</t>
+          <t>#YiBiYaYa #益生菌 #iOiO #兒童健康 #隨身包</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>粉末包裝撕開倒入水杯的動作特寫，或產品包裝平鋪，清爽背景</t>
+          <t>產品包裝平鋪＋手撕開包裝的動作特寫，強調免沖泡的便利感，清爽背景</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr"/>

--- a/iOiO_7-9月社群月曆.xlsx
+++ b/iOiO_7-9月社群月曆.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="165" customHeight="1">
+    <row r="2" ht="180" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>7月</t>
@@ -676,19 +676,19 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>孩子暑假在家，飲料怎麼給才不踩雷？</t>
+          <t>孩子放暑假，冰箱開關次數直接乘三</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>孩子放暑假的第一個挑戰：他每隔20分鐘就打開冰箱。
-飲料這件事，很多爸媽沒有刻意想過，但細節其實不少。
-幾個選飲料的簡單原則：
-✦ 成分表越短越好——五個字以內的材料名你看得懂，超過十個字就要停一下
-✦「果汁飲料」跟「果汁」不一樣——前者果汁含量可能不到10%
-✦ 甜味來源看清楚——砂糖、果糖、麥芽糖漿都是糖，代糖另算
-✦「天然香料」不代表是真的水果
-今年暑假，從成分表開始選。</t>
+          <t>孩子放暑假，冰箱開關次數大概會暴增三倍。（你懂的。）
+飲料這件事，大部分時候都是「就給吧」——但翻一下成分表，有幾個坑值得知道：
+✦「果汁飲料」≠「果汁」，前者果汁含量可能不到10%
+✦ 成分表越短越好，你念得出來的材料名越多越安心
+✦ 甜味來源先看清楚——砂糖、果糖、麥芽糖漿都是糖，代糖另算
+✦「天然香料」不等於真水果，只是來源比較天然的香料
+不是要你每次都當成分偵探，就是知道這幾件事，選起來比較有底。
+今年暑假，孩子要飲料，你可以更輕鬆說「這個可以」。</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr"/>
     </row>
-    <row r="3" ht="105" customHeight="1">
+    <row r="3" ht="135" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>7月</t>
@@ -731,15 +731,16 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>YiBiYaYa 益生菌系列——撕開，直接吃</t>
+          <t>YiBiYaYa 益生菌——孩子的事能省力就省力</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>YiBiYaYa 益生菌系列是粉末包裝，不是飲料罐。
-100億益生菌配方，草莓蘋果或葡萄藍莓口味——撕開一包直接倒入口中就好，不用加水、不用沖泡，孩子吃起來是水果甜味，不是藥水感，不用哄。
-不加人工色素、不加人工香料，成分表翻開看得懂。一包一份量，書包塞一包帶出門，下課了撕開就吃。
-給孩子好的，不用麻煩。</t>
+          <t>孩子的事情已經夠多了，益生菌這件事可以更省力一點嗎？
+可以。
+YiBiYaYa 益生菌是粉末包裝——撕開直接倒入口中，不用泡水、不用找杯子、不用哄他「快喝完」。草莓蘋果或葡萄藍莓口味，孩子吃起來是水果甜味，不是藥水感。
+100億益生菌配方，不加人工色素香料，成分表看得懂。
+一包一份量，書包塞一包，下課撕開就吃。完成。</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -754,7 +755,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr"/>
     </row>
-    <row r="4" ht="120" customHeight="1">
+    <row r="4" ht="150" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>7月</t>
@@ -782,16 +783,17 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>真果汁 vs. 果味飲料怎麼分辨？成分表這樣看</t>
+          <t>超市飲料架有個祕密，包裝越健康越要翻背面</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>超市架上很多「看起來健康」的飲料，但分辨真假靠的不是包裝顏色，是成分表三行字。
-真果汁的成分表：水果、水（或不含水）、就這樣。
-果味飲料的成分表：水、糖、果汁（含量5%）、香料、色素⋯⋯
-一個快速檢查法：把飲料翻到背面，找到「果汁含量」那行。台灣法規規定，超過10%才能叫做「含果汁」，100%才是純果汁。
-下次站在飲料架前，花10秒翻到背面，就能判斷大半。</t>
+          <t>超市的飲料架，有一件沒人說破的事：
+包裝看起來越健康的，成分表越要翻開看。
+真果汁的成分表：水果、水，差不多這樣。
+果味飲料的成分表：水、糖、果汁（含量5%）、香料、色素……
+一個快速判斷法：找「果汁含量」那行。台灣規定，超過10%才能叫「含果汁」，100%才是純果汁。
+下次站在飲料架前，花10秒翻到背面——比研究哪個包裝好看更值得。</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -806,7 +808,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr"/>
     </row>
-    <row r="5" ht="210" customHeight="1">
+    <row r="5" ht="180" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>7月</t>
@@ -834,21 +836,19 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>孩子不愛喝水，媽媽試過的5件事</t>
+          <t>「媽媽我不渴。」夏天聽到這句話的頻率跟蚊子一樣高</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>「媽媽，我不渴。」
-這句話在夏天出現的頻率，大概跟蚊子一樣高。
-孩子不愛喝水是真的，因為白開水沒有刺激感，而夏天流汗消耗大，等他說渴通常已經有點晚了。
-試過有效的幾個方法：
-✦ 換成有顏色的杯子，莫名其妙就喝了
-✦ 把補水變成一件「有儀式感的小事」，不是一直叫他喝
-✦ 讓孩子自己選想喝什麼，選擇感會提高接受度
-✦ 戶外玩完回家，什麼都別說，直接遞給他
-✦ 跟孩子一起喝，不是叫他喝
-你家有用哪個方法？</t>
+這句話在夏天出現的頻率，大概跟「媽媽我要吃冰」一樣高。
+孩子不愛喝水是真的，等他說渴通常已經有點晚了。幾個有點用的方法：
+✦ 換個有顏色或奇怪形狀的杯子，莫名其妙就喝了
+✦ 讓他自己選——選擇感這件事，小孩在意得要命
+✦ 戶外回來什麼都別說，直接遞給他，比問「你要不要喝水」有效得多
+✦ 你自己先喝，他通常就跟著了
+你家有用哪個方法？或有更厲害的招，留言告訴我們。</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr"/>
     </row>
-    <row r="6" ht="105" customHeight="1">
+    <row r="6" ht="135" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>7月</t>
@@ -891,15 +891,16 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>YiBiYaYa 綜合莓果汁——618第一名的那包</t>
+          <t>618賣最好的那包，是草莓藍莓覆盆子這個</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>618排行榜第一名，就是這包。
-草莓、藍莓、覆盆子、黑醋栗——這四種莓果加在一起，顏色深、酸甜感明顯，孩子通常不用勸就喜歡。
-包裝是100ml的小包裝，剛好一口氣喝完，不會喝一半剩在那裡放到壞。
-你家孩子喝過了嗎？</t>
+草莓、藍莓、覆盆子、黑醋栗——四種莓果加在一起，顏色深、酸甜感明顯，孩子通常不用勸就喜歡。
+而且是那種「你遞過去，他拿著就走」的類型，不用追在後面說「快喝快喝」。
+100ml 小包裝，一口氣喝完剛好，不會喝一半放到壞。
+你家孩子試過了嗎？</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -914,7 +915,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr"/>
     </row>
-    <row r="7" ht="105" customHeight="1">
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>7月</t>
@@ -942,15 +943,16 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>我們的果汁原料是這樣來的</t>
+          <t>「天然原料」這四個字，我們說的時候具體是什麼意思</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>我們常說「真材實料」，但這句話到底是什麼意思？
-iOiO的果汁原料，從選擇優質水果開始，經過萃取濃縮的工藝保留水果原有的香氣與風味層次，呈現真實水果應有的滋味——不是香料調出來的甜，是水果本身的酸甜比例。
-有人問過我們：為什麼不直接用鮮榨？因為鮮榨的品質穩定性很難控制，每一批水果的成熟度不同，孩子喝到的口味就不一樣。我們選擇用有品質標準的原料工藝，讓每一包的味道都跟上次一樣。
-好原料不是一句話，是每次選料時的取捨。</t>
+          <t>「天然原料」——幾乎每個品牌都在說。
+我們說的時候，具體是什麼？
+iOiO的果汁原料選擇真實水果，透過萃取濃縮的工藝保留水果的香氣與風味——不是香料調出來的甜，是水果本身的酸甜比例。
+有人問過：為什麼不直接鮮榨？因為鮮榨的品質穩定性很難控制，每批水果成熟度不同，孩子喝到的口味就不一樣。我們選擇有品質標準的工藝，讓每一包的味道都跟上次一樣。
+好原料，是每次選料時做的選擇，不是包裝上的一句話。</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -965,7 +967,7 @@
       </c>
       <c r="J7" s="13" t="inlineStr"/>
     </row>
-    <row r="8" ht="165" customHeight="1">
+    <row r="8" ht="180" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>7月</t>
@@ -993,19 +995,19 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>孩子挑食怎麼辦？試試這幾件事</t>
+          <t>孩子挑食不是故意的，但你可以這樣應對</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>「不要！我不吃那個。」
-孩子挑食的背後，大多不是故意的。大部分的情況是：不熟悉、質地不對、顏色不喜歡，或是上次有個不好的記憶。
-幾個讓孩子主動想吃的小方法：
-✦ 讓他參與——幫忙洗水果、選顏色，參與過的東西接受度高很多
-✦ 不要反覆強調「這個很健康」——孩子聽到「健康」兩個字通常會自動關掉
-✦ 換個形式再試——不喜歡吃整顆葡萄，打成果汁可能就接受了
-✦ 新食物搭著他已經喜歡的東西一起出現，不要單獨登場
-挑食是過程，不是戰場。</t>
+          <t>「不要——我不吃那個。」
+你家幾歲的孩子說這句話說得最熟練？
+孩子挑食，大部分時候不是故意的。通常是：不熟悉這個食物、質地不對、或是某次有不好的記憶。幾個讓孩子主動想吃的方式：
+✦ 讓他參與——洗水果、選顏色，自己碰過的東西接受度高很多
+✦ 別一直說「這個很健康」——孩子聽到「健康」兩個字會自動關掉
+✦ 換個形式再試——不吃整顆葡萄，打成果汁可能就接受了
+✦ 新食物跟他已經喜歡的東西一起出現，不要單獨登場
+挑食是過程，不是你輸了的戰場。</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1048,15 +1050,15 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>帶孩子出門，那個永遠忘不了的清單</t>
+          <t>帶孩子出門的包包，永遠比預期重兩公斤</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>帶孩子出門，永遠有個必備清單。
-防曬、換洗衣物、OK繃（永遠要帶）、帽子、孩子指定要帶的那個玩具、他喝習慣的飲料。
+          <t>帶孩子出門，你的包包有多重？
+防曬、換洗衣物、OK繃（永遠要帶）、他指定要帶的那個玩具、帽子、他習慣喝的飲料——
 每個家庭的清單長得不一樣，但有幾格是固定的。
-你家的出門清單上，飲料這格通常放什麼？</t>
+你家出門包包，飲料這格通常放什麼？</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -1099,14 +1101,14 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>今年暑假，你們去了哪裡？</t>
+          <t>今年暑假帶孩子去了哪裡？</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
           <t>暑假快到一半了。
-今年帶孩子去了哪裡，還是都在家裡？
-留言說說你們這個夏天最難忘的一個地方，或一件事。</t>
+今年帶孩子去哪裡了，還是都在家裡神遊？
+留言說說你們這個夏天最難忘的一個地方——或是某個下午什麼都沒做，你卻記住了的那個時刻。</t>
         </is>
       </c>
       <c r="H10" s="16" t="inlineStr">
@@ -1125,7 +1127,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="255" customHeight="1">
+    <row r="11" ht="225" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>7月</t>
@@ -1153,22 +1155,21 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>夏天補水的4個誤解，你中了幾個？</t>
+          <t>補水這件事，你可能中了幾個誤解？</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>夏天到了，「多喝水」這句話大家都知道。
-但幾個關於補水的常見誤解，可能你也有：
+          <t>夏天「多喝水」這句話大家都會說，但有幾個補水誤解可能你也有：
 誤解一：口渴才喝水就夠了
-孩子感到口渴時，身體其實已經有點缺水了，不要等他說渴。
+孩子感到口渴時，身體已經有點缺水了，不要等他說渴。
 誤解二：運動飲料比水更能補水
-運動飲料是高強度運動後補充電解質用的，一般戶外玩耍不需要，含糖量通常也不低。
+一般戶外玩耍不需要運動飲料，那是高強度運動後補充電解質用的，含糖量也不低。
 誤解三：喝果汁等於喝水
-果汁的含糖量讓身體需要額外的水分來代謝，不能替代白開水。
+果汁有含糖量，身體需要額外水分代謝，沒辦法替代白開水。
 誤解四：一次喝很多就夠了
-少量多次比一次灌大量更有效，孩子的腸胃容量有限。
-今天讓孩子多喝一杯水吧。</t>
+少量多次比一次灌大量有效，孩子腸胃容量有限。
+你中了幾個？</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1211,16 +1212,16 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>暑假剩幾天了</t>
+          <t>暑假剩幾天了，你記住了哪一個下午？</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>暑假剩幾天了。
-一開始覺得漫長的假期，突然就快到尾聲了。
-這個夏天，孩子有沒有做到一件讓你覺得「還好我陪他做了這件事」的事情？
-可能是去了一個地方，學了一樣東西，或是某個下午什麼都沒做，就坐在那裡喝著飲料，他說了一句話你記住了。
-暑假快結束了。不用急著打卡，慢慢記住就好。</t>
+一開始覺得好長的假期，突然就快過了一半。
+這個夏天，有沒有一件讓你覺得「還好有做」的事？
+可能是去了某個地方，學了什麼，或只是某個下午，孩子說了一句話，你現在還記得。
+不用打卡，不用精彩，記住就好。</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -1263,16 +1264,16 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>開學前，先把飲食作息調回來</t>
+          <t>開學前兩週，現在只需要做一件事</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>開學前兩週，孩子的飲食作息可以開始慢慢調整了。
-暑假期間孩子的生活節奏通常比較鬆，飲食時間不固定，零食頻率可能也比較高。離開學還有一段時間，但現在開始做一件事：把正餐時間固定下來。
-不需要突然變得很嚴格，只要三餐的時間點開始規律，身體會慢慢跟上。
-飲料的部分也可以注意：暑假喝慣了甜的或碳酸飲料的孩子，開學後突然只有白開水，接受度會很低。這段時間可以在飲品選擇上慢慢過渡，讓孩子覺得喝的東西沒有突然變得「很無趣」。
-開學不用一夜變身，慢慢來。</t>
+          <t>離開學還有兩週——現在做一件事就好。
+把正餐時間固定下來。
+暑假孩子的生活節奏比較鬆，飲食時間不固定，零食頻率也高。不需要突然變嚴格，只要三餐時間點規律，身體會慢慢跟上。
+飲料的部分也注意一下：暑假喝慣了甜飲的孩子，開學後突然只有白開水，接受度會很低。這段時間慢慢過渡，比突然斷掉有效。
+開學不用一夜變身。現在開始，兩週後會輕鬆很多。</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1287,7 +1288,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr"/>
     </row>
-    <row r="14" ht="135" customHeight="1">
+    <row r="14" ht="165" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>8月</t>
@@ -1315,16 +1316,17 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>iOiO不加人工色素，所以顏色不是最鮮豔的那種</t>
+          <t>iOiO顏色不是最好看的，因為我們不加色素</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>iOiO的產品沒有加人工色素，所以顏色不是最鮮豔的那種。
-莓果汁是深紅色，不是亮紅色。蔬果汁是帶點土的綠，不是螢光綠。
-曾經有人問：「為什麼不做得漂亮一點？」
-因為那個漂亮需要靠色素才做得到，而我們不想加。顏色來自水果本身，深一點、暗一點，是真的。
-你可能偶爾會覺得包裝不夠吸睛——但打開來喝那一口，應該讓你覺得值得。</t>
+          <t>先說一件有點奇怪的事：
+iOiO的產品顏色，不是最漂亮的那種。
+莓果汁是深紅色，不是鮮豔亮紅。蔬果汁帶點土的綠，不是螢光感。
+有人問過：為什麼不做得好看一點？
+因為那個「好看」需要靠人工色素才做得到，而我們不加。顏色來自水果本身，深一點、暗一點，是真的樣子。
+可能你偶爾會覺得包裝不夠吸睛——但打開來喝那一口，應該讓你覺得選對了。</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -1367,22 +1369,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>孩子零食成分表，4件事先看清楚</t>
+          <t>幫孩子選零食，成分表看這4件事就夠了</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>在超市選孩子的零食，你會翻到背面看嗎？
-成分表要看什麼——簡單說4件事：
+          <t>你在超市幫孩子選零食，會翻到背面嗎？
+成分表看什麼，說簡單一點：
 1. 成分表越短越好
-排在最前面的是含量最多的成分，如果第二個就是糖，要考慮一下。
-2.「天然香料」跟「香料」不一樣，但都不是真的水果
-真的水果就是水果，不需要「香料」兩個字。
-3. 色素的全名通常很長
-「紅色7號」「黃色4號」這類代號都是人工色素，出現了就先放回去。
-4. 份量單位要注意
-很多飲料的熱量是「每100ml」，但整瓶是500ml，要自己乘以5。
-這4件事，下次帶孩子一起看，也是一堂很好的食育課。</t>
+排最前面的是含量最多的。如果第二個就是糖，先停一下。
+2.「天然香料」不是真水果
+真的水果就直接寫水果名，不需要「香料」兩個字。
+3. 色素認代號
+「紅色7號」「黃色4號」這類代號都是人工色素，出現了可以先放回去。
+4. 份量單位要自己換算
+很多飲料熱量標的是「每100ml」，但整瓶500ml，要乘以5。
+下次帶孩子逛超市，把成分表翻給他看，順便解釋——這比買任何教材都有用。</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1425,15 +1427,15 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>開學前一天晚上，你在做什麼？</t>
+          <t>開學前一天晚上，你有沒有那個感覺</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
           <t>孩子開學前一天晚上，你通常在做什麼？
-幫他整理書包、確認文具齊全、提醒他早點睡——這些事好像每年都一樣，但每次做還是有點感觸。
+整理書包、確認文具、提醒他早點睡——這些事好像每年都一樣，但每次做，還是有點感觸。
 上一個年級結束了，下一個年級要開始了。
-孩子好像沒有特別感覺，但你有。</t>
+孩子沒什麼感覺，但你有。</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -1476,16 +1478,16 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>這口感，是蒟蒻嗎？——超口感蒟蒻</t>
+          <t>「這真的是蒟蒻？」——對，但咀嚼感升級了</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>很多人第一次喝iOiO超口感蒟蒻，都會說同一句話：
+          <t>很多人第一次喝iOiO超口感蒟蒻，都說同一句話：
 「這真的是蒟蒻？」
-是的，蒟蒻。但咀嚼感升級了。
-一般蒟蒻飲料的口感通常很軟，嚼一下就沒了。超口感系列在這件事上認真了一點——每一顆蒟蒻塊的嚼勁明顯一些，喝下去有種真實的飽足感，不是那種喝了半瓶還沒感覺的感覺。
-不想喝含糖飲料，又覺得白開水太無聊，這個可以試試。</t>
+是的，蒟蒻。但咀嚼感升級了——每一顆蒟蒻塊嚼勁更明顯，喝下去有真實的飽足感，不是那種喝了半瓶還沒感覺的感覺。
+不想喝含糖飲料，又覺得白開水太無趣——超口感蒟蒻可以試試。
+你喝過哪個口味？</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -1528,21 +1530,21 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>開學後孩子特別累？放學前30分鐘最重要</t>
+          <t>開學第一週孩子特別累，放學後先做這件事</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>開學第一週，孩子放學回來通常像是被抽乾了。
-這是正常的——從暑假的鬆散節奏切換回上課模式，大腦在適應，身體也在適應。
-這段時間的飲食可以注意幾件事：
-放學後別急著讓孩子做功課
-讓他先吃點東西、喘一口氣，然後再開始。空腹做功課專注力不好，這不是偷懶，是生理需求。
-點心選擇影響接下來的狀態
-含糖量高的點心會讓血糖快速升高再下降，孩子反而更難進入學習狀態。
-補水不能忘
-孩子在學校通常喝水量不夠，放學後的補水很重要。
-這週開始，多留意孩子放學回家的前30分鐘。</t>
+          <t>開學第一週，孩子放學回來通常像被抽乾了。
+正常的。從暑假的鬆散切換回上課模式，大腦和身體都在適應。
+這段時間幾件事可以注意：
+別急著叫他寫功課
+讓他先吃點東西、喘一口氣再開始。空腹做功課專注力不好，不是偷懶，是生理需求。
+點心選擇影響後面的狀態
+含糖量高的點心讓血糖快速升高再下降，孩子反而更難靜下來。
+補水別忘記
+孩子在學校的喝水量通常不夠，放學後補水很重要。
+放學後那30分鐘，先把人顧好。</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1585,15 +1587,15 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>陪孩子長大的每個夏天</t>
+          <t>每年夏天都比上一個快，謝謝你讓iOiO在場</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
           <t>每年夏天都比上一個快。
-去年還說要去某個地方，今年暑假轉眼又快結束了。
+去年說要去的地方，今年暑假又快結束了。
 孩子在長，夏天在縮短，你陪在旁邊的時間是固定的。
-謝謝你把iOiO帶進這個夏天。不管是出門時包包裡的那一包，還是下午在家裡沒事喝的那一口，我們都在。
+謝謝你把iOiO帶進這個夏天。不管是出門包包裡的那一包，還是下午在家沒事喝的那一口，我們都在。
 明年夏天再見。</t>
         </is>
       </c>
@@ -1641,7 +1643,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>開學第一天放學，孩子說了什麼？</t>
+          <t>開學第一天放學，孩子說「還好」就夠了</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -1651,8 +1653,8 @@
 「還可以。」
 「不知道。」
 通常就這樣。
-但如果你繼續等，繼續問，或是什麼都不說，只是遞給他一杯他喜歡喝的東西，他可能就開始說了。
-有時候讓孩子說話的不是問題，是安靜。</t>
+但如果你繼續等，什麼都不說，就遞給他一杯他喜歡喝的東西——他可能就開始說了。
+有時候讓孩子說話的，不是問題，是安靜。</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -1667,7 +1669,7 @@
       </c>
       <c r="J20" s="10" t="inlineStr"/>
     </row>
-    <row r="21" ht="105" customHeight="1">
+    <row r="21" ht="135" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>9月</t>
@@ -1695,15 +1697,16 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>孩子書包裡的零食，你上次檢查是什麼時候？</t>
+          <t>孩子書包裡的零食，你上次翻是什麼時候？</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>孩子書包裡的零食，你上次檢查是什麼時候？
-小學生的書包是一個奇妙的地方。餅乾、糖果、同學分享的零食、偶爾一包說不清楚從哪裡來的飲料——這些都會出現。
-不用變成「零食警察」，但知道孩子平常在吃什麼，是基本的。
-一個簡單的習慣：每週一次，跟孩子一起清書包，順便聊聊「你最近在學校喝的是什麼」。這不是審問，是對話的開始。</t>
+          <t>孩子書包是一個奇妙的地方。
+餅乾、糖果、同學分享的零食、一包說不清楚從哪來的飲料——都會出現。
+不用變成零食警察，但知道孩子平常在吃什麼，是基本的。
+一個簡單的習慣：每週一次，跟孩子一起清書包，順便聊聊「你最近在學校喝什麼吃什麼」。
+不是審問，是對話的開始。</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1746,16 +1749,16 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>「嚴選原料」——我們說這句話的具體意思</t>
+          <t>「嚴選原料」不是一句話，是每次選料時的選擇</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>「嚴選原料」——這句話很多品牌都在說。
-我們說的時候是什麼意思？
-十全食品累積了超過70年的食品品管標準，iOiO的原料選擇沿用同一套規範：原料來源要可追溯、加工工藝要有明確品質控制、每一批原料進廠前都要通過檢驗。
+          <t>「嚴選原料」——幾乎每個食品品牌都在說。
+我們說的時候，具體是什麼？
+十全食品做了70年，iOiO的原料選擇用同一套規範：來源要可追溯、加工工藝要有品質控制、每批原料進廠都要通過檢驗。
 不是每次選最貴的，是每次選最符合標準的。
-這件事做起來比說起來花時間，也不是每次消費者都看得見——但我們知道放進包裝裡的是什麼，這件事讓我們安心。</t>
+這件事做起來比說起來花時間，消費者不一定每次看得見——但我們知道放進包裝裡的是什麼，這讓我們安心。</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
@@ -1798,17 +1801,17 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>元素蒟蒻，因為你的一天不只需要水</t>
+          <t>元素蒟蒻，你的一天可以多一個選擇</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>iOiO元素蒟蒻，有兩個口味。
-Bright Berry，藍莓口味
-Energy Apple，蘋果口味
-系列名字叫「元素」，是因為每一瓶加入了特定的成分——不是靠廣告說的那種，就是你翻到成分表、找得到、看得懂的那些。
+          <t>iOiO元素蒟蒻，兩個口味。
+Bright Berry，藍莓口味。
+Energy Apple，蘋果口味。
+系列叫「元素」，是因為每一瓶加入了特定成分——不是靠廣告說的那種，就是你翻到成分表、找得到、念得出來的那些。
 口味是果汁感，蒟蒻塊的嚼感在，不甜膩，帶得出門。
-你的一天喝什麼，可以多一個選擇。</t>
+你今天喝的是什麼？</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -1851,22 +1854,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>課後點心的4個常見地雷</t>
+          <t>課後點心踩這幾個雷，孩子晚餐就廢了</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>課後點心這件事，大部分爸媽都沒有特別規劃，通常是孩子要什麼就給什麼。
-但有幾個常見的地雷：
-地雷一：空腹讓孩子吃高糖點心
-血糖快速升高再下降，反而讓孩子更沒辦法靜下來寫功課。
-地雷二：點心分量跟正餐一樣多
-課後點心的目的是補充到下一餐的能量，不是吃飽，吃太多正餐就吃不下了。
-地雷三：讓孩子一邊看電視一邊吃
+          <t>課後點心這件事，大部分都沒有特別規劃，孩子要什麼給什麼。
+但有幾個狀況很常見：
+空腹讓孩子吃高糖點心
+血糖快速升高再下降，孩子反而更沒辦法靜下來寫功課。
+點心吃得太多
+課後點心是補充到下一餐的能量，不是吃飽，吃太多正餐就吃不下了。
+邊看電視邊吃
 不知道吃了多少，不知道吃的是什麼，這個習慣很難改。
-地雷四：每天都一樣的點心
-孩子很快就膩，然後會開始要求更甜、更刺激的東西。
-課後點心不用複雜，但稍微想一下，孩子的狀態會不一樣。</t>
+每天都一樣
+孩子很快膩，然後開始要求更甜、更刺激的。
+課後點心不用複雜，稍微想一下，孩子的狀態會不一樣。</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1909,16 +1912,16 @@
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>放學後那20分鐘，讓他靜一下</t>
+          <t>放學後那20分鐘，什麼都不用說</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>放學後的那段時間，其實是孩子一天裡狀態最放鬆的時候。
-書包放下了，學校的事暫時結束了，功課還沒開始——這個中間地帶，大概20分鐘。
+          <t>放學後有一段時間，大概20分鐘。
+書包放下了，學校的事暫時結束了，功課還沒開始——就這個中間地帶。
 什麼都不用說，給他一杯他喜歡的飲料，讓他坐著發呆一下。
-後來他可能會開始說話，說今天發生了什麼，說誰說了什麼，說有一件事他覺得很好笑——
-但這些都是在那20分鐘之後的事。
+後來他可能會開始說話，說今天誰說了什麼，說有一件事他覺得很好笑——
+但這些都是那20分鐘之後的事。
 先讓他靜一下。</t>
         </is>
       </c>
@@ -1962,13 +1965,13 @@
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>孩子課後最愛的點心是什麼？</t>
+          <t>你家孩子放學第一件事是翻冰箱還是找零食？</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>孩子放學回家，第一件事是翻冰箱還是找零食？
-你家孩子課後最愛的點心是什麼？留言說說——說不定可以給別的爸媽一點靈感。</t>
+          <t>孩子放學回家，第一件事是翻冰箱還是直接找零食？
+你家孩子課後最愛什麼點心——留言說說，說不定可以給其他爸媽靈感（或是證明大家的孩子都一樣）。</t>
         </is>
       </c>
       <c r="H26" s="16" t="inlineStr">
@@ -2015,18 +2018,18 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>有些東西，我們永遠不加</t>
+          <t>有些東西我們從來不加，這不是意外</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>有些東西，我們永遠不加。
-不加人工色素——所以顏色不是最鮮豔的
-不加人工香料——所以味道不是最濃的
-不加防腐劑——所以保存方式要注意
+          <t>有些東西，我們從來不加。
+不加人工色素——所以顏色不是最鮮豔的那種
+不加人工香料——所以味道不是最濃的那種
+不加防腐劑——所以保存要注意
 不加代糖——有甜味是來自水果本身
-這些「不加」的背後，每一個都是我們做過的選擇，不是意外。
-選擇iOiO，不是因為最便宜，是因為你知道裡面放了什麼——和沒放什麼。</t>
+每一個「不加」背後，都是我們做過的選擇，不是意外。
+選iOiO，不是因為最便宜，是因為你知道裡面有什麼——和沒有什麼。</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -2069,20 +2072,20 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>雙十連假帶孩子出門，飲食這樣準備</t>
+          <t>雙十連假帶孩子出門，吃喝先想好這幾件事</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>雙十連假到了，帶孩子出門玩一玩。
-戶外活動時有幾件吃喝的事可以提前想好：
-飲料選擇先備著
-出門在外的選擇不多，加油站和便利超商的飲料選項有限，提前準備孩子習慣喝的東西，比現場碰運氣好。
+          <t>雙十連假，帶孩子出去透透氣。
+出門前有幾件吃喝的事先想好：
+飲料先備著
+外出的選擇不多，便利超商飲料選項有限，孩子習慣喝的東西提前準備，比現場碰運氣好。
 零食備量別多
-吃太多零食孩子午餐就吃不下了，然後下午又餓——這個循環你應該不陌生。
-天氣換季注意補水
-秋天溫差大，孩子容易忽略補水，戶外活動量一大，補水需求跟夏天差不多。
-連假玩得好，吃喝準備好一半。</t>
+吃太多零食孩子午餐就吃不下了，然後下午又餓——這個循環你應該很熟悉。
+換季補水需求還是高
+秋天溫差大，孩子容易忽略補水，戶外活動量一大，需求跟夏天差不多。
+準備好吃喝，出門才真的放鬆。</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2125,15 +2128,15 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>連假結束，元素蒟蒻陪你收假</t>
+          <t>收假週四，帶瓶元素蒟蒻出門吧</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
           <t>雙十連假結束的週四。
-返回工作模式的那一天，通常是最難的那一天。
+返回工作模式的那天，通常是最難的那天。
 iOiO元素蒟蒻——Bright Berry 藍莓口味、Energy Apple 蘋果口味，加了特定成分配方，口感是蒟蒻，喝起來是果汁感。
-不用說什麼特別的話，就是一瓶你可以帶著走的東西。
+不用說什麼特別的話，就是一瓶可以帶著走的東西。
 收假了，慢慢來。</t>
         </is>
       </c>
